--- a/data/trans_orig/P04B3_3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023</t>
+          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39774</t>
+          <t>41135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28060</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61125</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54465</t>
+          <t>53963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84447</t>
+          <t>82432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>80916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108276</t>
+          <t>108944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142339</t>
+          <t>144721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181334</t>
+          <t>184302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>410978</t>
+          <t>413442</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>443754</t>
+          <t>444202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>620334</t>
+          <t>619657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>654922</t>
+          <t>655582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1043582</t>
+          <t>1043860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1090229</t>
+          <t>1090042</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>43133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>68555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102650</t>
+          <t>100447</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183645</t>
+          <t>181854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>162165</t>
+          <t>161770</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>895478</t>
+          <t>860882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>302927</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1222082</t>
+          <t>1154587</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2076125</t>
+          <t>2077513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2165309</t>
+          <t>2164193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1328081</t>
+          <t>1356677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2051148</t>
+          <t>2049671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3264444</t>
+          <t>3330699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4172891</t>
+          <t>4171969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56643</t>
+          <t>56878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90670</t>
+          <t>92168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>585482</t>
+          <t>585986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>615274</t>
+          <t>614671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,77 +1883,77 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>616569</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>604136</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>627005</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,68%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>95,15%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>616569</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>603586</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>626655</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1218378</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1195856</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1235317</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>91,6%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1579</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1218378</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1197325</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1235406</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35090</t>
+          <t>35269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>71638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>73185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82921</t>
+          <t>82383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130797</t>
+          <t>132741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199050</t>
+          <t>192970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294061</t>
+          <t>294875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>288863</t>
+          <t>289183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1062024</t>
+          <t>1075400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>536245</t>
+          <t>535139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1426204</t>
+          <t>1458578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3100387</t>
+          <t>3102253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3218360</t>
+          <t>3220333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2557930</t>
+          <t>2527643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3309983</t>
+          <t>3308189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5569455</t>
+          <t>5586676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6461948</t>
+          <t>6461306</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18303</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>28260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41135</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39483</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>51251</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67283</t>
+          <t>83096</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82432</t>
+          <t>100400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93980</t>
+          <t>106327</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80916</t>
+          <t>92560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108944</t>
+          <t>122028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>161264</t>
+          <t>189423</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144721</t>
+          <t>168267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184302</t>
+          <t>211940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>429352</t>
+          <t>476437</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>413442</t>
+          <t>457092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>444202</t>
+          <t>493150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>639772</t>
+          <t>695748</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>619657</t>
+          <t>677781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>655582</t>
+          <t>710470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1069125</t>
+          <t>1172185</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1043860</t>
+          <t>1147929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1090042</t>
+          <t>1195919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754932</t>
+          <t>821441</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754932</t>
+          <t>821441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754932</t>
+          <t>821441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1269871</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1269871</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1269871</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27152</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35577</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>77154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148222</t>
+          <t>166972</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100447</t>
+          <t>139706</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181854</t>
+          <t>197629</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>360711</t>
+          <t>184958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161770</t>
+          <t>160192</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>860882</t>
+          <t>212168</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>508933</t>
+          <t>351930</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>315634</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1154587</t>
+          <t>397822</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2113949</t>
+          <t>2029953</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2077513</t>
+          <t>1998162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2164193</t>
+          <t>2060610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1853819</t>
+          <t>1958520</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1356677</t>
+          <t>1930546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2049671</t>
+          <t>1984951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3967768</t>
+          <t>3988473</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3330699</t>
+          <t>3940304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4171969</t>
+          <t>4026087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237088</t>
+          <t>2170688</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237088</t>
+          <t>2170688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237088</t>
+          <t>2170688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4526410</t>
+          <t>4400320</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4526410</t>
+          <t>4400320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4526410</t>
+          <t>4400320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>42151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>29691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>57128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24625</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44838</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71685</t>
+          <t>78771</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>63234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92168</t>
+          <t>97818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>601809</t>
+          <t>661479</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>585986</t>
+          <t>645524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614671</t>
+          <t>675701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>616569</t>
+          <t>684813</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604136</t>
+          <t>670896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627005</t>
+          <t>695598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1218378</t>
+          <t>1346292</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195856</t>
+          <t>1326526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1235317</t>
+          <t>1364581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658959</t>
+          <t>732477</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658959</t>
+          <t>732477</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658959</t>
+          <t>732477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305582</t>
+          <t>1444064</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305582</t>
+          <t>1444064</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305582</t>
+          <t>1444064</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>51713</t>
+          <t>59661</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>45274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71638</t>
+          <t>80898</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>57620</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73185</t>
+          <t>72737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>104710</t>
+          <t>117281</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82383</t>
+          <t>97297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132741</t>
+          <t>141441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>254060</t>
+          <t>292218</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192970</t>
+          <t>257836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294875</t>
+          <t>331682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>487822</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289183</t>
+          <t>295381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1075400</t>
+          <t>364701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>741882</t>
+          <t>620124</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535139</t>
+          <t>575396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1458578</t>
+          <t>670528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3145110</t>
+          <t>3167869</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3102253</t>
+          <t>3128897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3220333</t>
+          <t>3206273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3110160</t>
+          <t>3339081</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2527643</t>
+          <t>3299370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3308189</t>
+          <t>3374697</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6255271</t>
+          <t>6506950</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5586676</t>
+          <t>6452624</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6461306</t>
+          <t>6555347</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3450884</t>
+          <t>3519749</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3450884</t>
+          <t>3519749</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450884</t>
+          <t>3519749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3650979</t>
+          <t>3724606</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3650979</t>
+          <t>3724606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3650979</t>
+          <t>3724606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7101864</t>
+          <t>7244355</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7101864</t>
+          <t>7244355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7101864</t>
+          <t>7244355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
